--- a/AfterToken/Configs/GameConfig/Datas/weapon.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/weapon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP9"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +627,31 @@
           <t>reloadSound</t>
         </is>
       </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>aimAssistRadius</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>aimAssistMaxAngle</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>lockOnRange</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>lockOnAngle</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>lockOnHoldTime</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -839,6 +864,31 @@
           <t>string</t>
         </is>
       </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1057,6 +1107,21 @@
         <is>
           <t>换弹音效</t>
         </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -1140,7 +1205,6 @@
       <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
@@ -1153,7 +1217,6 @@
       <c r="AD5" t="n">
         <v>-1</v>
       </c>
-      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="b">
         <v>1</v>
       </c>
@@ -1178,11 +1241,21 @@
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -1265,7 +1338,6 @@
       <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
@@ -1278,7 +1350,6 @@
       <c r="AD6" t="n">
         <v>-1</v>
       </c>
-      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="b">
         <v>1</v>
       </c>
@@ -1303,11 +1374,21 @@
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -1390,7 +1471,6 @@
       <c r="Y7" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
@@ -1403,7 +1483,6 @@
       <c r="AD7" t="n">
         <v>-1</v>
       </c>
-      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="b">
         <v>1</v>
       </c>
@@ -1428,11 +1507,21 @@
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -1515,7 +1604,6 @@
       <c r="Y8" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
@@ -1528,7 +1616,6 @@
       <c r="AD8" t="n">
         <v>-1</v>
       </c>
-      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="b">
         <v>1</v>
       </c>
@@ -1553,11 +1640,21 @@
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -1657,7 +1754,6 @@
       <c r="AD9" t="n">
         <v>-1</v>
       </c>
-      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="b">
         <v>1</v>
       </c>
@@ -1687,10 +1783,21 @@
           <t>SFX_LockOn</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AfterToken/Configs/GameConfig/Datas/weapon.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/weapon.xlsx
@@ -896,6 +896,11 @@
           <t>##group</t>
         </is>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>锁定保持时间</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1121,7 +1126,7 @@
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1254,7 +1259,7 @@
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1387,7 +1392,7 @@
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1520,7 +1525,7 @@
         <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1653,7 +1658,7 @@
         <v>10</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1796,7 +1801,7 @@
         <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/AfterToken/Configs/GameConfig/Datas/weapon.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/weapon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU9"/>
+  <dimension ref="A1:AV9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,140 +514,145 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
+          <t>scopeFov</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>aimSensitivityMultiplier</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>aimAssistEnabled</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>tracerSpeed</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>tracerDelay</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>projectileSpeed</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>projectileLifeTime</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>projectilePrefab</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>explosionRadius</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>explosionDamageFalloff</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>recoilIntensity</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>raycastRadius</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>hitLayers</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>showDebugRay</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>debugRayDuration</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>debugHitColor</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>debugMissColor</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>trackingTime</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>trackingLaserColor</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>lockOnSound</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>muzzleEffect</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>hitEffect</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>fireSound</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>reloadSound</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>aimAssistRadius</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>aimAssistMaxAngle</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>lockOnRange</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>lockOnAngle</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>lockOnHoldTime</t>
         </is>
@@ -756,14 +761,14 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>float</t>
@@ -781,14 +786,14 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="AB2" t="inlineStr">
         <is>
           <t>float</t>
@@ -806,69 +811,69 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>cfg.Color</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>cfg.Color</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
           <t>cfg.Color</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="AR2" t="inlineStr">
         <is>
           <t>float</t>
@@ -885,6 +890,11 @@
         </is>
       </c>
       <c r="AU2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -896,7 +906,7 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>锁定保持时间</t>
         </is>
@@ -1000,132 +1010,137 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>狙击镜FOV</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>瞄准灵敏度系数</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>是否开启辅助瞄准</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>曳光速度</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>曳光延迟</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>投掷物速度</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>投掷物生命周期</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>投掷物Prefab</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>爆炸半径</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>爆炸伤害衰减</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>后坐力强度</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>射线检测半径</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>命中层级</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>显示Debug射线</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>Debug射线持续时间</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>Debug命中颜色</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Debug未命中颜色</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>锁定时间</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>锁定激光颜色</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>锁定音效</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>枪口特效</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>命中特效</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>开火音效</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>换弹音效</t>
         </is>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>2</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>15</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>20</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>10</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1193,72 +1208,75 @@
         <v>50</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>0.8</v>
       </c>
-      <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>40</v>
       </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>-1</v>
       </c>
-      <c r="AF5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AG5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0,1,0,1</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
         <v>2</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
         <v>15</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
         <v>20</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>10</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1326,72 +1344,75 @@
         <v>45</v>
       </c>
       <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>0.7</v>
       </c>
-      <c r="U6" t="b">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>50</v>
       </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
         <v>0.3</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>-1</v>
       </c>
-      <c r="AF6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AG6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>0,1,0,1</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
         <v>2</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
         <v>15</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
         <v>20</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>10</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1459,72 +1480,75 @@
         <v>40</v>
       </c>
       <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>0.6</v>
       </c>
-      <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>60</v>
       </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
         <v>0.6</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>-1</v>
       </c>
-      <c r="AF7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AG7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>0,1,0,1</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
         <v>2</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>15</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
         <v>20</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>10</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1592,72 +1616,75 @@
         <v>25</v>
       </c>
       <c r="T8" t="n">
+        <v>75</v>
+      </c>
+      <c r="U8" t="n">
         <v>0.4</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
         <v>100</v>
       </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>-1</v>
       </c>
-      <c r="AF8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AG8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>0,1,0,1</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
         <v>2</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
         <v>15</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
         <v>20</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>10</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1725,82 +1752,85 @@
         <v>35</v>
       </c>
       <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="V9" t="b">
         <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>10</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>5</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Projectile_Rocket</t>
         </is>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>3</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>2</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>-1</v>
       </c>
-      <c r="AF9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AG9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>0,1,0,1</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AK9" t="n">
         <v>1.5</v>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>1,0,0,1</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>SFX_LockOn</t>
         </is>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
         <v>2</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AS9" t="n">
         <v>15</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
         <v>20</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>10</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>1</v>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/weapon.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/weapon.xlsx
@@ -1616,7 +1616,7 @@
         <v>25</v>
       </c>
       <c r="T8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0.4</v>
